--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0003T0006Z000C1N45_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0003T0006Z000C1N45_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>32.70037398900389</v>
+        <v>5.313810773213132</v>
       </c>
       <c r="D2" t="n">
-        <v>31.70052252833499</v>
+        <v>5.151334910854436</v>
       </c>
       <c r="E2" t="n">
-        <v>10.46910838798436</v>
+        <v>1.701230113047459</v>
       </c>
       <c r="F2" t="n">
-        <v>10.1241261497517</v>
+        <v>1.645170499334651</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>31.45115083558016</v>
+        <v>5.110812010781776</v>
       </c>
       <c r="D3" t="n">
-        <v>30.36615815594657</v>
+        <v>4.934500700341318</v>
       </c>
       <c r="E3" t="n">
-        <v>10.46910838798436</v>
+        <v>1.701230113047459</v>
       </c>
       <c r="F3" t="n">
-        <v>10.1241261497517</v>
+        <v>1.645170499334651</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>24.93796808944491</v>
+        <v>4.052419814534797</v>
       </c>
       <c r="D4" t="n">
-        <v>23.94698679422301</v>
+        <v>3.89138535406124</v>
       </c>
       <c r="E4" t="n">
-        <v>10.46910838798436</v>
+        <v>1.701230113047459</v>
       </c>
       <c r="F4" t="n">
-        <v>10.1241261497517</v>
+        <v>1.645170499334651</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>20.74327225989444</v>
+        <v>3.370781742232846</v>
       </c>
       <c r="D5" t="n">
-        <v>19.93212138916475</v>
+        <v>3.238969725739271</v>
       </c>
       <c r="E5" t="n">
-        <v>10.46910838798436</v>
+        <v>1.701230113047459</v>
       </c>
       <c r="F5" t="n">
-        <v>10.1241261497517</v>
+        <v>1.645170499334651</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>16.13441720439531</v>
+        <v>2.621842795714237</v>
       </c>
       <c r="D6" t="n">
-        <v>15.83025535110804</v>
+        <v>2.572416494555057</v>
       </c>
       <c r="E6" t="n">
-        <v>10.46910838798436</v>
+        <v>1.701230113047459</v>
       </c>
       <c r="F6" t="n">
-        <v>10.1241261497517</v>
+        <v>1.645170499334651</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>16.27891404902045</v>
+        <v>2.645323532965823</v>
       </c>
       <c r="D7" t="n">
-        <v>15.20268258190524</v>
+        <v>2.470435919559602</v>
       </c>
       <c r="E7" t="n">
-        <v>10.46910838798436</v>
+        <v>1.701230113047459</v>
       </c>
       <c r="F7" t="n">
-        <v>10.1241261497517</v>
+        <v>1.645170499334651</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>21.18934903289646</v>
+        <v>3.443269217845674</v>
       </c>
       <c r="D8" t="n">
-        <v>21.55820381313693</v>
+        <v>3.503208119634752</v>
       </c>
       <c r="E8" t="n">
-        <v>10.46910838798436</v>
+        <v>1.701230113047459</v>
       </c>
       <c r="F8" t="n">
-        <v>10.1241261497517</v>
+        <v>1.645170499334651</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>2.757293309850225</v>
+        <v>0.4480601628506615</v>
       </c>
       <c r="D9" t="n">
-        <v>3.354083402788251</v>
+        <v>0.5450385529530909</v>
       </c>
       <c r="E9" t="n">
-        <v>10.46910838798436</v>
+        <v>1.701230113047459</v>
       </c>
       <c r="F9" t="n">
-        <v>10.1241261497517</v>
+        <v>1.645170499334651</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>22.70038766828803</v>
+        <v>3.688812996096805</v>
       </c>
       <c r="D10" t="n">
-        <v>22.18793365141449</v>
+        <v>3.605539218354854</v>
       </c>
       <c r="E10" t="n">
-        <v>10.46910838798436</v>
+        <v>1.701230113047459</v>
       </c>
       <c r="F10" t="n">
-        <v>10.1241261497517</v>
+        <v>1.645170499334651</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>20.40446222303302</v>
+        <v>3.315725111242866</v>
       </c>
       <c r="D11" t="n">
-        <v>20.61080649678111</v>
+        <v>3.349256055726931</v>
       </c>
       <c r="E11" t="n">
-        <v>10.46910838798436</v>
+        <v>1.701230113047459</v>
       </c>
       <c r="F11" t="n">
-        <v>10.1241261497517</v>
+        <v>1.645170499334651</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>38.86588640085954</v>
+        <v>6.315706540139675</v>
       </c>
       <c r="D12" t="n">
-        <v>36.09016486523718</v>
+        <v>5.864651790601042</v>
       </c>
       <c r="E12" t="n">
-        <v>10.46910838798436</v>
+        <v>1.701230113047459</v>
       </c>
       <c r="F12" t="n">
-        <v>10.1241261497517</v>
+        <v>1.645170499334651</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>44.408932637061</v>
+        <v>7.216451553522413</v>
       </c>
       <c r="D13" t="n">
-        <v>44.79500780232838</v>
+        <v>7.279188767878361</v>
       </c>
       <c r="E13" t="n">
-        <v>10.46910838798436</v>
+        <v>1.701230113047459</v>
       </c>
       <c r="F13" t="n">
-        <v>10.1241261497517</v>
+        <v>1.645170499334651</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>12.16730877301048</v>
+        <v>1.977187675614203</v>
       </c>
       <c r="D14" t="n">
-        <v>13.60542151547417</v>
+        <v>2.210880996264553</v>
       </c>
       <c r="E14" t="n">
-        <v>10.46910838798436</v>
+        <v>1.701230113047459</v>
       </c>
       <c r="F14" t="n">
-        <v>10.1241261497517</v>
+        <v>1.645170499334651</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>18.46461737182094</v>
+        <v>3.000500322920903</v>
       </c>
       <c r="D15" t="n">
-        <v>15.42618230099723</v>
+        <v>2.50675462391205</v>
       </c>
       <c r="E15" t="n">
-        <v>10.46910838798436</v>
+        <v>1.701230113047459</v>
       </c>
       <c r="F15" t="n">
-        <v>10.1241261497517</v>
+        <v>1.645170499334651</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
